--- a/data/raw/infrastructure/standard_data/2024-data.xlsx
+++ b/data/raw/infrastructure/standard_data/2024-data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Academic\Chapter2\2. dMFA\TRIPI-fut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A927E36-1789-4CC4-8A78-38D64E938E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256E1C1F-E906-4505-B367-A149F3EB4F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E7782B8E-F493-42B0-9CFA-BB4F41381E91}"/>
+    <workbookView xWindow="-20" yWindow="14290" windowWidth="25820" windowHeight="13900" xr2:uid="{E7782B8E-F493-42B0-9CFA-BB4F41381E91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Brazil</t>
   </si>
@@ -144,6 +147,30 @@
   </si>
   <si>
     <t>urban_tunnels</t>
+  </si>
+  <si>
+    <t>rail_bridge</t>
+  </si>
+  <si>
+    <t>rail_tunnel</t>
+  </si>
+  <si>
+    <t>rail_highspeed</t>
+  </si>
+  <si>
+    <t>rail_electrified</t>
+  </si>
+  <si>
+    <t>rail_bridge_share</t>
+  </si>
+  <si>
+    <t>rail_tunnel_share</t>
+  </si>
+  <si>
+    <t>rail_highspeed_share</t>
+  </si>
+  <si>
+    <t>rail_electrified_share</t>
   </si>
 </sst>
 </file>
@@ -196,6 +223,434 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Original_input"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Cleaned"/>
+      <sheetName val="High speed rail"/>
+      <sheetName val="Sheet5"/>
+      <sheetName val="Sheet6"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Brazil</v>
+          </cell>
+          <cell r="M2">
+            <v>270.17209330658505</v>
+          </cell>
+          <cell r="N2">
+            <v>231.86958669220971</v>
+          </cell>
+          <cell r="R2">
+            <v>2037.2757390894376</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Canada</v>
+          </cell>
+          <cell r="M3">
+            <v>361.53856570277526</v>
+          </cell>
+          <cell r="N3">
+            <v>135.400713740442</v>
+          </cell>
+          <cell r="R3">
+            <v>334.01559149406847</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Central America</v>
+          </cell>
+          <cell r="M4">
+            <v>45.095654242703262</v>
+          </cell>
+          <cell r="N4">
+            <v>3.9424863643968924</v>
+          </cell>
+          <cell r="R4">
+            <v>165.43105121767235</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Central Asia</v>
+          </cell>
+          <cell r="M5">
+            <v>178.89929687887604</v>
+          </cell>
+          <cell r="N5">
+            <v>27.3504431348811</v>
+          </cell>
+          <cell r="Q5">
+            <v>850.78345049516588</v>
+          </cell>
+          <cell r="R5">
+            <v>16003.76808295157</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Central Europe</v>
+          </cell>
+          <cell r="M6">
+            <v>1063.3667136362455</v>
+          </cell>
+          <cell r="N6">
+            <v>761.65800529627245</v>
+          </cell>
+          <cell r="Q6">
+            <v>834.22522478204451</v>
+          </cell>
+          <cell r="R6">
+            <v>68427.513625936772</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>China</v>
+          </cell>
+          <cell r="M7">
+            <v>48355.410583730132</v>
+          </cell>
+          <cell r="N7">
+            <v>27399.189800361131</v>
+          </cell>
+          <cell r="Q7">
+            <v>141691.44024145542</v>
+          </cell>
+          <cell r="R7">
+            <v>212191.394093176</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Eastern Africa</v>
+          </cell>
+          <cell r="M8">
+            <v>102.624674469787</v>
+          </cell>
+          <cell r="N8">
+            <v>43.031258718024255</v>
+          </cell>
+          <cell r="R8">
+            <v>1976.1523727975296</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>India</v>
+          </cell>
+          <cell r="M9">
+            <v>1156.6409998434242</v>
+          </cell>
+          <cell r="N9">
+            <v>278.85372161526902</v>
+          </cell>
+          <cell r="R9">
+            <v>81086.594687368299</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Indonesia region</v>
+          </cell>
+          <cell r="M10">
+            <v>248.71121912798114</v>
+          </cell>
+          <cell r="N10">
+            <v>15.946535436227981</v>
+          </cell>
+          <cell r="R10">
+            <v>1903.7672705318835</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>Japan</v>
+          </cell>
+          <cell r="M11">
+            <v>6291.4909531935664</v>
+          </cell>
+          <cell r="N11">
+            <v>5074.155086298766</v>
+          </cell>
+          <cell r="Q11">
+            <v>6246.5560960152498</v>
+          </cell>
+          <cell r="R11">
+            <v>34424.769586062648</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>Korea</v>
+          </cell>
+          <cell r="M12">
+            <v>1479.0091408191031</v>
+          </cell>
+          <cell r="N12">
+            <v>2359.4578373621002</v>
+          </cell>
+          <cell r="Q12">
+            <v>1429.4194526482149</v>
+          </cell>
+          <cell r="R12">
+            <v>13149.018790556151</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>Mexico</v>
+          </cell>
+          <cell r="M13">
+            <v>193.14765126192449</v>
+          </cell>
+          <cell r="N13">
+            <v>104.83580572930251</v>
+          </cell>
+          <cell r="R13">
+            <v>1043.4154331261038</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>Middle East</v>
+          </cell>
+          <cell r="M14">
+            <v>125.84765712375733</v>
+          </cell>
+          <cell r="N14">
+            <v>269.949239453026</v>
+          </cell>
+          <cell r="R14">
+            <v>668.87591195190805</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>Northern Africa</v>
+          </cell>
+          <cell r="M15">
+            <v>155.87964062864219</v>
+          </cell>
+          <cell r="N15">
+            <v>98.221297482022962</v>
+          </cell>
+          <cell r="Q15">
+            <v>1827.106541899888</v>
+          </cell>
+          <cell r="R15">
+            <v>3355.4195053780122</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>Oceania</v>
+          </cell>
+          <cell r="M16">
+            <v>485.10188697675505</v>
+          </cell>
+          <cell r="N16">
+            <v>532.05052014279772</v>
+          </cell>
+          <cell r="R16">
+            <v>8898.1061617334763</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>Rest of South America</v>
+          </cell>
+          <cell r="M17">
+            <v>237.8717306328976</v>
+          </cell>
+          <cell r="N17">
+            <v>110.88806089362414</v>
+          </cell>
+          <cell r="R17">
+            <v>3154.6565815194167</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>Rest of South Asia</v>
+          </cell>
+          <cell r="M18">
+            <v>89.72165737979725</v>
+          </cell>
+          <cell r="N18">
+            <v>27.433825021221182</v>
+          </cell>
+          <cell r="R18">
+            <v>108.53843007131726</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>Rest of Southern Africa</v>
+          </cell>
+          <cell r="M19">
+            <v>84.599282847313802</v>
+          </cell>
+          <cell r="N19">
+            <v>11.812530269307354</v>
+          </cell>
+          <cell r="R19">
+            <v>255.92931451432656</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>Russia region</v>
+          </cell>
+          <cell r="M20">
+            <v>1259.3954321122033</v>
+          </cell>
+          <cell r="N20">
+            <v>251.09610517993525</v>
+          </cell>
+          <cell r="Q20">
+            <v>6652.6341991034087</v>
+          </cell>
+          <cell r="R20">
+            <v>108839.7691410523</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>South Africa</v>
+          </cell>
+          <cell r="M21">
+            <v>191.75050308282661</v>
+          </cell>
+          <cell r="N21">
+            <v>611.03338396863626</v>
+          </cell>
+          <cell r="Q21">
+            <v>792.57114809486347</v>
+          </cell>
+          <cell r="R21">
+            <v>16564.555858609885</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>South Eastern Asia</v>
+          </cell>
+          <cell r="M22">
+            <v>451.30511274873646</v>
+          </cell>
+          <cell r="N22">
+            <v>225.75213855623966</v>
+          </cell>
+          <cell r="R22">
+            <v>868.57258962181731</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>Turkey</v>
+          </cell>
+          <cell r="M23">
+            <v>154.53627571179968</v>
+          </cell>
+          <cell r="N23">
+            <v>479.88729960018622</v>
+          </cell>
+          <cell r="Q23">
+            <v>2781.1783357588661</v>
+          </cell>
+          <cell r="R23">
+            <v>8324.5365079455132</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Ukraine region</v>
+          </cell>
+          <cell r="M24">
+            <v>300.36232303630612</v>
+          </cell>
+          <cell r="N24">
+            <v>62.478952710481394</v>
+          </cell>
+          <cell r="R24">
+            <v>21798.745047585879</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>USA</v>
+          </cell>
+          <cell r="M25">
+            <v>3643.3115574602762</v>
+          </cell>
+          <cell r="N25">
+            <v>948.18622916927552</v>
+          </cell>
+          <cell r="Q25">
+            <v>2710.6404475619011</v>
+          </cell>
+          <cell r="R25">
+            <v>10032.242813506229</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Western Africa</v>
+          </cell>
+          <cell r="M26">
+            <v>85.213355433542887</v>
+          </cell>
+          <cell r="N26">
+            <v>14.695214793713621</v>
+          </cell>
+          <cell r="R26">
+            <v>189.4425306568148</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Western Europe</v>
+          </cell>
+          <cell r="M27">
+            <v>6263.5797846430414</v>
+          </cell>
+          <cell r="N27">
+            <v>10018.458667827455</v>
+          </cell>
+          <cell r="Q27">
+            <v>36183.830977635356</v>
+          </cell>
+          <cell r="R27">
+            <v>216360.2108358297</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,8 +970,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8145D969-B82C-4BA2-B01F-1D91EC977BC5}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -1426,6 +1884,878 @@
       </c>
       <c r="AA11">
         <v>8655.1650000000009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12">
+        <f>_xlfn.XLOOKUP(B1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>270.17209330658505</v>
+      </c>
+      <c r="C12">
+        <f>_xlfn.XLOOKUP(C1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>361.53856570277526</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.XLOOKUP(D1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>45.095654242703262</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.XLOOKUP(E1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>178.89929687887604</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.XLOOKUP(F1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>1063.3667136362455</v>
+      </c>
+      <c r="G12">
+        <f>_xlfn.XLOOKUP(G1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>48355.410583730132</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.XLOOKUP(H1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>102.624674469787</v>
+      </c>
+      <c r="I12">
+        <f>_xlfn.XLOOKUP(I1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>1156.6409998434242</v>
+      </c>
+      <c r="J12">
+        <f>_xlfn.XLOOKUP(J1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>248.71121912798114</v>
+      </c>
+      <c r="K12">
+        <f>_xlfn.XLOOKUP(K1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>6291.4909531935664</v>
+      </c>
+      <c r="L12">
+        <f>_xlfn.XLOOKUP(L1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>1479.0091408191031</v>
+      </c>
+      <c r="M12">
+        <f>_xlfn.XLOOKUP(M1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>193.14765126192449</v>
+      </c>
+      <c r="N12">
+        <f>_xlfn.XLOOKUP(N1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>125.84765712375733</v>
+      </c>
+      <c r="O12">
+        <f>_xlfn.XLOOKUP(O1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>155.87964062864219</v>
+      </c>
+      <c r="P12">
+        <f>_xlfn.XLOOKUP(P1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>485.10188697675505</v>
+      </c>
+      <c r="Q12">
+        <f>_xlfn.XLOOKUP(Q1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>237.8717306328976</v>
+      </c>
+      <c r="R12">
+        <f>_xlfn.XLOOKUP(R1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>89.72165737979725</v>
+      </c>
+      <c r="S12">
+        <f>_xlfn.XLOOKUP(S1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>84.599282847313802</v>
+      </c>
+      <c r="T12">
+        <f>_xlfn.XLOOKUP(T1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>1259.3954321122033</v>
+      </c>
+      <c r="U12">
+        <f>_xlfn.XLOOKUP(U1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>191.75050308282661</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.XLOOKUP(V1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>451.30511274873646</v>
+      </c>
+      <c r="W12">
+        <f>_xlfn.XLOOKUP(W1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>154.53627571179968</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.XLOOKUP(X1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>3643.3115574602762</v>
+      </c>
+      <c r="Y12">
+        <f>_xlfn.XLOOKUP(Y1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>300.36232303630612</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.XLOOKUP(Z1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>85.213355433542887</v>
+      </c>
+      <c r="AA12">
+        <f>_xlfn.XLOOKUP(AA1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$M$2:$M$27)</f>
+        <v>6263.5797846430414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <f>_xlfn.XLOOKUP(B1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>231.86958669220971</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.XLOOKUP(C1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>135.400713740442</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.XLOOKUP(D1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>3.9424863643968924</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.XLOOKUP(E1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>27.3504431348811</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.XLOOKUP(F1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>761.65800529627245</v>
+      </c>
+      <c r="G13">
+        <f>_xlfn.XLOOKUP(G1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>27399.189800361131</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.XLOOKUP(H1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>43.031258718024255</v>
+      </c>
+      <c r="I13">
+        <f>_xlfn.XLOOKUP(I1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>278.85372161526902</v>
+      </c>
+      <c r="J13">
+        <f>_xlfn.XLOOKUP(J1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>15.946535436227981</v>
+      </c>
+      <c r="K13">
+        <f>_xlfn.XLOOKUP(K1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>5074.155086298766</v>
+      </c>
+      <c r="L13">
+        <f>_xlfn.XLOOKUP(L1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>2359.4578373621002</v>
+      </c>
+      <c r="M13">
+        <f>_xlfn.XLOOKUP(M1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>104.83580572930251</v>
+      </c>
+      <c r="N13">
+        <f>_xlfn.XLOOKUP(N1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>269.949239453026</v>
+      </c>
+      <c r="O13">
+        <f>_xlfn.XLOOKUP(O1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>98.221297482022962</v>
+      </c>
+      <c r="P13">
+        <f>_xlfn.XLOOKUP(P1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>532.05052014279772</v>
+      </c>
+      <c r="Q13">
+        <f>_xlfn.XLOOKUP(Q1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>110.88806089362414</v>
+      </c>
+      <c r="R13">
+        <f>_xlfn.XLOOKUP(R1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>27.433825021221182</v>
+      </c>
+      <c r="S13">
+        <f>_xlfn.XLOOKUP(S1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>11.812530269307354</v>
+      </c>
+      <c r="T13">
+        <f>_xlfn.XLOOKUP(T1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>251.09610517993525</v>
+      </c>
+      <c r="U13">
+        <f>_xlfn.XLOOKUP(U1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>611.03338396863626</v>
+      </c>
+      <c r="V13">
+        <f>_xlfn.XLOOKUP(V1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>225.75213855623966</v>
+      </c>
+      <c r="W13">
+        <f>_xlfn.XLOOKUP(W1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>479.88729960018622</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.XLOOKUP(X1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>948.18622916927552</v>
+      </c>
+      <c r="Y13">
+        <f>_xlfn.XLOOKUP(Y1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>62.478952710481394</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.XLOOKUP(Z1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>14.695214793713621</v>
+      </c>
+      <c r="AA13">
+        <f>_xlfn.XLOOKUP(AA1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$N$2:$N$27)</f>
+        <v>10018.458667827455</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <f>_xlfn.XLOOKUP(B1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.XLOOKUP(C1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>_xlfn.XLOOKUP(D1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.XLOOKUP(E1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>850.78345049516588</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.XLOOKUP(F1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>834.22522478204451</v>
+      </c>
+      <c r="G14">
+        <f>_xlfn.XLOOKUP(G1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>141691.44024145542</v>
+      </c>
+      <c r="H14">
+        <f>_xlfn.XLOOKUP(H1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f>_xlfn.XLOOKUP(I1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>_xlfn.XLOOKUP(J1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f>_xlfn.XLOOKUP(K1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>6246.5560960152498</v>
+      </c>
+      <c r="L14">
+        <f>_xlfn.XLOOKUP(L1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>1429.4194526482149</v>
+      </c>
+      <c r="M14">
+        <f>_xlfn.XLOOKUP(M1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f>_xlfn.XLOOKUP(N1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f>_xlfn.XLOOKUP(O1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>1827.106541899888</v>
+      </c>
+      <c r="P14">
+        <f>_xlfn.XLOOKUP(P1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f>_xlfn.XLOOKUP(Q1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f>_xlfn.XLOOKUP(R1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f>_xlfn.XLOOKUP(S1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f>_xlfn.XLOOKUP(T1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>6652.6341991034087</v>
+      </c>
+      <c r="U14">
+        <f>_xlfn.XLOOKUP(U1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>792.57114809486347</v>
+      </c>
+      <c r="V14">
+        <f>_xlfn.XLOOKUP(V1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <f>_xlfn.XLOOKUP(W1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>2781.1783357588661</v>
+      </c>
+      <c r="X14">
+        <f>_xlfn.XLOOKUP(X1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>2710.6404475619011</v>
+      </c>
+      <c r="Y14">
+        <f>_xlfn.XLOOKUP(Y1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f>_xlfn.XLOOKUP(Z1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f>_xlfn.XLOOKUP(AA1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$Q$2:$Q$27)</f>
+        <v>36183.830977635356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15">
+        <f>_xlfn.XLOOKUP(B1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>2037.2757390894376</v>
+      </c>
+      <c r="C15">
+        <f>_xlfn.XLOOKUP(C1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>334.01559149406847</v>
+      </c>
+      <c r="D15">
+        <f>_xlfn.XLOOKUP(D1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>165.43105121767235</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.XLOOKUP(E1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>16003.76808295157</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.XLOOKUP(F1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>68427.513625936772</v>
+      </c>
+      <c r="G15">
+        <f>_xlfn.XLOOKUP(G1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>212191.394093176</v>
+      </c>
+      <c r="H15">
+        <f>_xlfn.XLOOKUP(H1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>1976.1523727975296</v>
+      </c>
+      <c r="I15">
+        <f>_xlfn.XLOOKUP(I1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>81086.594687368299</v>
+      </c>
+      <c r="J15">
+        <f>_xlfn.XLOOKUP(J1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>1903.7672705318835</v>
+      </c>
+      <c r="K15">
+        <f>_xlfn.XLOOKUP(K1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>34424.769586062648</v>
+      </c>
+      <c r="L15">
+        <f>_xlfn.XLOOKUP(L1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>13149.018790556151</v>
+      </c>
+      <c r="M15">
+        <f>_xlfn.XLOOKUP(M1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>1043.4154331261038</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.XLOOKUP(N1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>668.87591195190805</v>
+      </c>
+      <c r="O15">
+        <f>_xlfn.XLOOKUP(O1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>3355.4195053780122</v>
+      </c>
+      <c r="P15">
+        <f>_xlfn.XLOOKUP(P1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>8898.1061617334763</v>
+      </c>
+      <c r="Q15">
+        <f>_xlfn.XLOOKUP(Q1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>3154.6565815194167</v>
+      </c>
+      <c r="R15">
+        <f>_xlfn.XLOOKUP(R1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>108.53843007131726</v>
+      </c>
+      <c r="S15">
+        <f>_xlfn.XLOOKUP(S1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>255.92931451432656</v>
+      </c>
+      <c r="T15">
+        <f>_xlfn.XLOOKUP(T1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>108839.7691410523</v>
+      </c>
+      <c r="U15">
+        <f>_xlfn.XLOOKUP(U1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>16564.555858609885</v>
+      </c>
+      <c r="V15">
+        <f>_xlfn.XLOOKUP(V1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>868.57258962181731</v>
+      </c>
+      <c r="W15">
+        <f>_xlfn.XLOOKUP(W1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>8324.5365079455132</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.XLOOKUP(X1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>10032.242813506229</v>
+      </c>
+      <c r="Y15">
+        <f>_xlfn.XLOOKUP(Y1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>21798.745047585879</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.XLOOKUP(Z1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>189.4425306568148</v>
+      </c>
+      <c r="AA15">
+        <f>_xlfn.XLOOKUP(AA1,[1]Sheet5!$A$2:$A$27,[1]Sheet5!$R$2:$R$27)</f>
+        <v>216360.2108358297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <f>B12/B$4</f>
+        <v>6.327436661432281E-3</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:I16" si="0">C12/C$4</f>
+        <v>4.9395095738625928E-3</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>4.5224614615762783E-3</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>2.6409786360579667E-3</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>6.7217470650322974E-3</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0.14035833381595433</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>7.8550448627576451E-3</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>9.3795768237302547E-3</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16:AA16" si="1">J12/J$4</f>
+        <v>2.8232497950091324E-2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>0.12557655688598912</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>7.3580603871647346E-2</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="1"/>
+        <v>7.9630705319741861E-3</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>3.8415146313790665E-3</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="1"/>
+        <v>6.726434937922892E-3</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>7.0505898891550277E-3</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="1"/>
+        <v>3.845961214718416E-3</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>5.7598784964041812E-3</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>3.3821703969707747E-3</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="1"/>
+        <v>4.6381640549428534E-3</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="1"/>
+        <v>5.5893948312738329E-3</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="1"/>
+        <v>1.9561137875496265E-2</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="1"/>
+        <v>9.9413500628130341E-3</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="1"/>
+        <v>8.0738010906141171E-3</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="1"/>
+        <v>4.0830698126167716E-3</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="1"/>
+        <v>3.9457831126601473E-3</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="1"/>
+        <v>1.5898129943036594E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17">
+        <f t="shared" ref="B17:H19" si="2">B13/B$4</f>
+        <v>5.4303910724138394E-3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>1.8499081018609231E-3</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>3.9537607215577486E-4</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>4.0375751758736075E-4</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>4.8145878519664674E-3</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>7.9529975691690666E-2</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>3.2936763938824806E-3</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17:AA17" si="3">I13/I$4</f>
+        <v>2.2613152264424076E-3</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>1.8101737854563651E-3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>0.10127884305698434</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>0.11738286646872631</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>4.3221592902866835E-3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>8.2402324905314784E-3</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="3"/>
+        <v>4.2383929316667937E-3</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="3"/>
+        <v>7.7329528467042115E-3</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="3"/>
+        <v>1.7928619774931404E-3</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="3"/>
+        <v>1.7611745416712223E-3</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="3"/>
+        <v>4.7224975018143552E-4</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>9.2474920877588654E-4</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="3"/>
+        <v>1.7811201447616613E-2</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="3"/>
+        <v>9.7848851768832616E-3</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="3"/>
+        <v>3.087124763457217E-2</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="3"/>
+        <v>2.1012386370021976E-3</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="3"/>
+        <v>8.4932731628008348E-4</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="3"/>
+        <v>6.8045824595148194E-4</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="3"/>
+        <v>2.542871061059521E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>1.2559584950133597E-2</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>5.2732993090216307E-3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>0.41127919767813953</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18:AA18" si="4">I14/I$4</f>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="4"/>
+        <v>0.1246796685823109</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>7.1113520267688107E-2</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="4"/>
+        <v>7.8842324944933609E-2</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="4"/>
+        <v>2.4500651682700336E-2</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="4"/>
+        <v>2.3102901986466563E-2</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="4"/>
+        <v>0.17891376827570027</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="4"/>
+        <v>6.0069449062006642E-3</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="4"/>
+        <v>9.1841289885014735E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>4.7713044834474992E-2</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>4.5634777822311399E-3</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>1.6590413560770782E-2</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>0.23625363733048899</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>0.43254357408815569</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>0.615915161622546</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>0.15125763491254252</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ref="I19:AA19" si="5">I15/I$4</f>
+        <v>0.65755748270016889</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="5"/>
+        <v>0.21610647783076004</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="5"/>
+        <v>0.68710963241820033</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="5"/>
+        <v>0.65416278792768834</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="5"/>
+        <v>4.3017818926858915E-2</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="5"/>
+        <v>2.0417516392962753E-2</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>0.14479126909287646</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="5"/>
+        <v>0.12932725891365643</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="5"/>
+        <v>5.1005164951710806E-2</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="5"/>
+        <v>6.9678624722108538E-3</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="5"/>
+        <v>1.0231724455981752E-2</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="5"/>
+        <v>0.40084050815687855</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="5"/>
+        <v>0.48284537151106371</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="5"/>
+        <v>3.7646965878555233E-2</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="5"/>
+        <v>0.53551912749916597</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="5"/>
+        <v>2.2232063245630172E-2</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="5"/>
+        <v>0.29632810452717373</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="5"/>
+        <v>8.7720890050882894E-3</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="5"/>
+        <v>0.54916243819617006</v>
       </c>
     </row>
   </sheetData>
